--- a/港岛-香港仔及鸭脷洲-滶晨 II/滶晨 II_销控明细表.xlsx
+++ b/港岛-香港仔及鸭脷洲-滶晨 II/滶晨 II_销控明细表.xlsx
@@ -764,7 +764,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H3" s="5" t="n">
@@ -826,7 +826,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -888,7 +888,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -950,7 +950,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2214,7 +2214,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2478,7 +2478,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-03-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3238,7 +3238,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3688,7 +3688,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3812,7 +3812,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3998,7 +3998,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4122,7 +4122,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4324,7 +4324,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-01-14</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-01-11</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6146,7 +6146,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6208,7 +6208,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6518,7 +6518,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6580,7 +6580,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -6774,7 +6774,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-01-04</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2026-01-16</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7464,7 +7464,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -7836,7 +7836,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -7898,7 +7898,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -7960,7 +7960,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8022,7 +8022,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8146,7 +8146,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8456,7 +8456,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8518,7 +8518,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -8650,7 +8650,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -8712,7 +8712,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -9146,7 +9146,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -9208,7 +9208,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -9270,7 +9270,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>2026-02-19</t>
+          <t>2026-02-20</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -9332,7 +9332,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -9518,7 +9518,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -9580,7 +9580,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -9704,7 +9704,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="G148" s="3" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="H148" s="5" t="n">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>2025-10-14</t>
+          <t>2025-10-15</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -10200,7 +10200,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -10324,7 +10324,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>2025-12-07</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -10510,7 +10510,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -10634,7 +10634,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -10696,7 +10696,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -10758,7 +10758,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -10820,7 +10820,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -10882,7 +10882,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -11068,7 +11068,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -11130,7 +11130,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -11192,7 +11192,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -11254,7 +11254,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -11440,7 +11440,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -11626,7 +11626,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -11688,7 +11688,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -11750,7 +11750,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G179" s="3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H179" s="5" t="n">
@@ -11874,7 +11874,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -12122,7 +12122,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -12308,7 +12308,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -12370,7 +12370,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
+          <t>2025-10-23</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -12432,7 +12432,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-22</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -12804,7 +12804,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -12866,7 +12866,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -13114,7 +13114,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>2025-10-15</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -13238,7 +13238,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -13300,7 +13300,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -13362,7 +13362,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -13424,7 +13424,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="G206" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H206" s="5" t="n">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -13610,7 +13610,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -13672,7 +13672,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -13982,7 +13982,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -14044,7 +14044,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -14106,7 +14106,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -14292,7 +14292,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -14354,7 +14354,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -14416,7 +14416,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -14602,7 +14602,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -14664,7 +14664,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -14726,7 +14726,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -14788,7 +14788,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>2025-10-12</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -14912,7 +14912,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -14974,7 +14974,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -15036,7 +15036,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -15098,7 +15098,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -15222,7 +15222,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -15284,7 +15284,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -15408,7 +15408,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -15470,7 +15470,7 @@
       </c>
       <c r="G238" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H238" s="5" t="n">
@@ -15532,7 +15532,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -15594,7 +15594,7 @@
       </c>
       <c r="G240" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H240" s="5" t="n">
@@ -15656,7 +15656,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -15780,7 +15780,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -15966,7 +15966,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -16028,7 +16028,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -16090,7 +16090,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-10</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -16214,7 +16214,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -16276,7 +16276,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -16338,7 +16338,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>2025-09-16</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -16400,7 +16400,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -16462,7 +16462,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -16586,7 +16586,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -16772,7 +16772,7 @@
       </c>
       <c r="G259" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H259" s="5" t="n">
@@ -16834,7 +16834,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -16896,7 +16896,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -16958,7 +16958,7 @@
       </c>
       <c r="G262" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H262" s="5" t="n">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -17082,7 +17082,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -17144,7 +17144,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -17330,7 +17330,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -17392,7 +17392,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -17454,7 +17454,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -17578,7 +17578,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -17640,7 +17640,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>2025-08-13</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -17826,7 +17826,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>2025-09-03</t>
+          <t>2025-09-04</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G277" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H277" s="5" t="n">
@@ -17950,7 +17950,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -18012,7 +18012,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -18136,7 +18136,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -18260,7 +18260,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-19</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -18384,7 +18384,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -18446,7 +18446,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -18508,7 +18508,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -18570,7 +18570,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>2025-08-11</t>
+          <t>2025-08-12</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -18632,7 +18632,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -18694,7 +18694,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -18756,7 +18756,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -18818,7 +18818,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>2025-09-14</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -18880,7 +18880,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -18942,7 +18942,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -19004,7 +19004,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -19066,7 +19066,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -19128,7 +19128,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -19314,7 +19314,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -19376,7 +19376,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -19438,7 +19438,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -19500,7 +19500,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -19562,7 +19562,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -19624,7 +19624,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -19748,7 +19748,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -19810,7 +19810,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -19872,7 +19872,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -19934,7 +19934,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -19996,7 +19996,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -20058,7 +20058,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -20182,7 +20182,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -20306,7 +20306,7 @@
       </c>
       <c r="G316" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H316" s="5" t="n">
@@ -20368,7 +20368,7 @@
       </c>
       <c r="G317" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H317" s="5" t="n">
@@ -20430,7 +20430,7 @@
       </c>
       <c r="G318" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H318" s="5" t="n">
@@ -20492,7 +20492,7 @@
       </c>
       <c r="G319" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H319" s="5" t="n">
@@ -20554,7 +20554,7 @@
       </c>
       <c r="G320" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H320" s="5" t="n">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -20678,7 +20678,7 @@
       </c>
       <c r="G322" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H322" s="5" t="n">
@@ -20740,7 +20740,7 @@
       </c>
       <c r="G323" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H323" s="5" t="n">
@@ -20802,7 +20802,7 @@
       </c>
       <c r="G324" s="3" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H324" s="5" t="n">
@@ -20864,7 +20864,7 @@
       </c>
       <c r="G325" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H325" s="5" t="n">
@@ -20926,7 +20926,7 @@
       </c>
       <c r="G326" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H326" s="5" t="n">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="G327" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H327" s="5" t="n">
@@ -21050,7 +21050,7 @@
       </c>
       <c r="G328" s="3" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-09</t>
         </is>
       </c>
       <c r="H328" s="5" t="n">
@@ -21112,7 +21112,7 @@
       </c>
       <c r="G329" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H329" s="5" t="n">
@@ -21174,7 +21174,7 @@
       </c>
       <c r="G330" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H330" s="5" t="n">
@@ -21236,7 +21236,7 @@
       </c>
       <c r="G331" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H331" s="5" t="n">
@@ -21298,7 +21298,7 @@
       </c>
       <c r="G332" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H332" s="5" t="n">
@@ -21360,7 +21360,7 @@
       </c>
       <c r="G333" s="3" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-07-25</t>
         </is>
       </c>
       <c r="H333" s="5" t="n">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="G334" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H334" s="5" t="n">
@@ -21484,7 +21484,7 @@
       </c>
       <c r="G335" s="3" t="inlineStr">
         <is>
-          <t>2026-01-13</t>
+          <t>2026-01-14</t>
         </is>
       </c>
       <c r="H335" s="5" t="n">
@@ -21546,7 +21546,7 @@
       </c>
       <c r="G336" s="3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="H336" s="5" t="n">
@@ -21608,7 +21608,7 @@
       </c>
       <c r="G337" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H337" s="5" t="n">
@@ -21670,7 +21670,7 @@
       </c>
       <c r="G338" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H338" s="5" t="n">
@@ -21732,7 +21732,7 @@
       </c>
       <c r="G339" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H339" s="5" t="n">
@@ -21794,7 +21794,7 @@
       </c>
       <c r="G340" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H340" s="5" t="n">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="G341" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H341" s="5" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="G342" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H342" s="5" t="n">
@@ -21980,7 +21980,7 @@
       </c>
       <c r="G343" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H343" s="5" t="n">
@@ -22042,7 +22042,7 @@
       </c>
       <c r="G344" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H344" s="5" t="n">
@@ -22104,7 +22104,7 @@
       </c>
       <c r="G345" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H345" s="5" t="n">
@@ -22166,7 +22166,7 @@
       </c>
       <c r="G346" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H346" s="5" t="n">
@@ -22228,7 +22228,7 @@
       </c>
       <c r="G347" s="3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H347" s="5" t="n">
@@ -22290,7 +22290,7 @@
       </c>
       <c r="G348" s="3" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="H348" s="5" t="n">
@@ -22352,7 +22352,7 @@
       </c>
       <c r="G349" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H349" s="5" t="n">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="G350" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H350" s="5" t="n">
@@ -22476,7 +22476,7 @@
       </c>
       <c r="G351" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H351" s="5" t="n">
@@ -22538,7 +22538,7 @@
       </c>
       <c r="G352" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H352" s="5" t="n">
@@ -22600,7 +22600,7 @@
       </c>
       <c r="G353" s="3" t="inlineStr">
         <is>
-          <t>2025-09-04</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="H353" s="5" t="n">
@@ -22662,7 +22662,7 @@
       </c>
       <c r="G354" s="3" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2025-09-03</t>
         </is>
       </c>
       <c r="H354" s="5" t="n">
@@ -22724,7 +22724,7 @@
       </c>
       <c r="G355" s="3" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H355" s="5" t="n">
@@ -22786,7 +22786,7 @@
       </c>
       <c r="G356" s="3" t="inlineStr">
         <is>
-          <t>2025-08-20</t>
+          <t>2025-08-21</t>
         </is>
       </c>
       <c r="H356" s="5" t="n">
@@ -22848,7 +22848,7 @@
       </c>
       <c r="G357" s="3" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="H357" s="5" t="n">
@@ -22910,7 +22910,7 @@
       </c>
       <c r="G358" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H358" s="5" t="n">
@@ -22972,7 +22972,7 @@
       </c>
       <c r="G359" s="3" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="H359" s="5" t="n">
@@ -23034,7 +23034,7 @@
       </c>
       <c r="G360" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H360" s="5" t="n">
@@ -23096,7 +23096,7 @@
       </c>
       <c r="G361" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H361" s="5" t="n">
@@ -23158,7 +23158,7 @@
       </c>
       <c r="G362" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H362" s="5" t="n">
@@ -23220,7 +23220,7 @@
       </c>
       <c r="G363" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H363" s="5" t="n">
@@ -23282,7 +23282,7 @@
       </c>
       <c r="G364" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="H364" s="5" t="n">
@@ -23344,7 +23344,7 @@
       </c>
       <c r="G365" s="3" t="inlineStr">
         <is>
-          <t>2025-09-24</t>
+          <t>2025-09-25</t>
         </is>
       </c>
       <c r="H365" s="5" t="n">
@@ -23406,7 +23406,7 @@
       </c>
       <c r="G366" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H366" s="5" t="n">
@@ -23468,7 +23468,7 @@
       </c>
       <c r="G367" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H367" s="5" t="n">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="G368" s="3" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="H368" s="5" t="n">
@@ -23592,7 +23592,7 @@
       </c>
       <c r="G369" s="3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="H369" s="5" t="n">
@@ -23654,7 +23654,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -23716,7 +23716,7 @@
       </c>
       <c r="G371" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H371" s="5" t="n">
@@ -23778,7 +23778,7 @@
       </c>
       <c r="G372" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="H372" s="5" t="n">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="G373" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="H373" s="5" t="n">
@@ -23902,7 +23902,7 @@
       </c>
       <c r="G374" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H374" s="5" t="n">
@@ -23964,7 +23964,7 @@
       </c>
       <c r="G375" s="3" t="inlineStr">
         <is>
-          <t>2025-08-17</t>
+          <t>2025-08-18</t>
         </is>
       </c>
       <c r="H375" s="5" t="n">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="G376" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H376" s="5" t="n">
@@ -24088,7 +24088,7 @@
       </c>
       <c r="G377" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H377" s="5" t="n">
@@ -24150,7 +24150,7 @@
       </c>
       <c r="G378" s="3" t="inlineStr">
         <is>
-          <t>2025-10-16</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="H378" s="5" t="n">
@@ -24212,7 +24212,7 @@
       </c>
       <c r="G379" s="3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H379" s="5" t="n">
@@ -24274,7 +24274,7 @@
       </c>
       <c r="G380" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H380" s="5" t="n">
@@ -24497,7 +24497,7 @@
           <t>D | 447呎 (2房)
 $1139万
 $25,483/呎
-(26年-01月-12日)</t>
+(26年-01月-13日)</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
@@ -24505,7 +24505,7 @@
           <t>E | 453呎 (2房)
 $1156万
 $25,523/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -24513,7 +24513,7 @@
           <t>F | 418呎 (1房)
 $1260万
 $30,153/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -24521,7 +24521,7 @@
           <t>G | 496呎 (2房)
 $1492万
 $30,091/呎
-(26年-06月-17日)</t>
+(26年-06月-18日)</t>
         </is>
       </c>
       <c r="I5" s="22" t="inlineStr">
@@ -24529,7 +24529,7 @@
           <t>H | 496呎 (2房)
 $1270万
 $25,595/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="J5" s="21" t="inlineStr"/>
@@ -24548,7 +24548,7 @@
           <t>A | 588呎 (2房)
 $1609万
 $27,369/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -24556,7 +24556,7 @@
           <t>B | 496呎 (2房)
 $1390万
 $28,026/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D6" s="22" t="inlineStr">
@@ -24564,7 +24564,7 @@
           <t>C | 591呎 (2房)
 $1654万
 $27,988/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
@@ -24572,7 +24572,7 @@
           <t>D | 448呎 (2房)
 $1170万
 $26,112/呎
-(26年-03月-02日)</t>
+(26年-03月-03日)</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
@@ -24580,7 +24580,7 @@
           <t>E | 453呎 (2房)
 $1150万
 $25,382/呎
-(26年-01月-29日)</t>
+(26年-01月-30日)</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -24588,7 +24588,7 @@
           <t>F | 418呎 (1房)
 $1159万
 $27,730/呎
-(26年-03月-18日)</t>
+(26年-03月-19日)</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
@@ -24596,7 +24596,7 @@
           <t>G | 496呎 (2房)
 $1319万
 $26,595/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr">
@@ -24604,7 +24604,7 @@
           <t>H | 494呎 (2房)
 $1348万
 $27,283/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="J6" s="21" t="inlineStr"/>
@@ -24623,7 +24623,7 @@
           <t>A | 588呎 (2房)
 $1601万
 $27,233/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -24631,7 +24631,7 @@
           <t>B | 496呎 (2房)
 $1363万
 $27,488/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -24639,7 +24639,7 @@
           <t>C | 591呎 (2房)
 $1645万
 $27,834/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -24647,7 +24647,7 @@
           <t>D | 448呎 (2房)
 $1163万
 $25,964/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -24655,7 +24655,7 @@
           <t>E | 453呎 (2房)
 $1144万
 $25,245/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
@@ -24663,7 +24663,7 @@
           <t>F | 505呎 (2房)
 $1388万
 $27,493/呎
-(26年-03月-03日)</t>
+(26年-03月-04日)</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
@@ -24671,7 +24671,7 @@
           <t>G | 498呎 (2房)
 $1371万
 $27,530/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr">
@@ -24679,7 +24679,7 @@
           <t>H | 494呎 (2房)
 $1341万
 $27,146/呎
-(26年-03月-11日)</t>
+(26年-03月-12日)</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr"/>
@@ -24712,7 +24712,7 @@
           <t>A | 588呎 (2房)
 $1593万
 $27,097/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -24720,7 +24720,7 @@
           <t>B | 496呎 (2房)
 $1378万
 $27,776/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -24728,7 +24728,7 @@
           <t>C | 591呎 (2房)
 $1638万
 $27,709/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -24736,7 +24736,7 @@
           <t>D | 448呎 (2房)
 $1178万
 $26,283/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -24744,7 +24744,7 @@
           <t>E | 453呎 (2房)
 $1137万
 $25,106/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
@@ -24752,7 +24752,7 @@
           <t>F | 505呎 (2房)
 $1440万
 $28,509/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
@@ -24760,7 +24760,7 @@
           <t>G | 498呎 (2房)
 $1364万
 $27,394/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr">
@@ -24768,7 +24768,7 @@
           <t>H | 494呎 (2房)
 $1283万
 $25,968/呎
-(26年-03月-01日)</t>
+(26年-03月-02日)</t>
         </is>
       </c>
       <c r="J8" s="21" t="inlineStr"/>
@@ -24801,7 +24801,7 @@
           <t>A | 588呎 (2房)
 $1585万
 $26,963/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -24809,7 +24809,7 @@
           <t>B | 496呎 (2房)
 $1372万
 $27,651/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -24817,7 +24817,7 @@
           <t>C | 591呎 (2房)
 $1606万
 $27,176/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -24825,7 +24825,7 @@
           <t>D | 448呎 (2房)
 $1117万
 $24,931/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -24833,7 +24833,7 @@
           <t>E | 453呎 (2房)
 $1186万
 $26,181/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -24841,7 +24841,7 @@
           <t>F | 505呎 (2房)
 $1436万
 $28,440/呎
-(26年-03月-12日)</t>
+(26年-03月-13日)</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
@@ -24849,7 +24849,7 @@
           <t>G | 498呎 (2房)
 $1267万
 $25,444/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr">
@@ -24857,7 +24857,7 @@
           <t>H | 494呎 (2房)
 $1277万
 $25,852/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="J9" s="21" t="inlineStr"/>
@@ -24890,7 +24890,7 @@
           <t>A | 588呎 (2房)
 $1577万
 $26,827/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -24898,7 +24898,7 @@
           <t>B | 496呎 (2房)
 $1345万
 $27,121/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -24906,7 +24906,7 @@
           <t>C | 591呎 (2房)
 $1599万
 $27,054/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -24914,7 +24914,7 @@
           <t>D | 448呎 (2房)
 $1111万
 $24,795/呎
-(25年-12月-15日)</t>
+(25年-12月-16日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -24922,7 +24922,7 @@
           <t>E | 453呎 (2房)
 $1180万
 $26,038/呎
-(26年-01月-01日)</t>
+(26年-01月-02日)</t>
         </is>
       </c>
       <c r="G10" s="22" t="inlineStr">
@@ -24930,7 +24930,7 @@
           <t>F | 505呎 (2房)
 $1330万
 $26,337/呎
-(26年-02月-12日)</t>
+(26年-02月-13日)</t>
         </is>
       </c>
       <c r="H10" s="22" t="inlineStr">
@@ -24938,7 +24938,7 @@
           <t>G | 498呎 (2房)
 $1298万
 $26,074/呎
-(26年-02月-26日)</t>
+(26年-02月-27日)</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr">
@@ -24946,7 +24946,7 @@
           <t>H | 494呎 (2房)
 $1233万
 $24,964/呎
-(26年-01月-26日)</t>
+(26年-01月-27日)</t>
         </is>
       </c>
       <c r="J10" s="21" t="inlineStr"/>
@@ -24979,7 +24979,7 @@
           <t>A | 588呎 (2房)
 $1570万
 $26,694/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -24987,7 +24987,7 @@
           <t>B | 496呎 (2房)
 $1339万
 $27,000/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -24995,7 +24995,7 @@
           <t>C | 591呎 (2房)
 $1592万
 $26,932/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -25003,7 +25003,7 @@
           <t>D | 448呎 (2房)
 $1105万
 $24,658/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -25011,7 +25011,7 @@
           <t>E | 453呎 (2房)
 $1173万
 $25,894/呎
-(25年-12月-30日)</t>
+(25年-12月-31日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -25019,7 +25019,7 @@
           <t>F | 505呎 (2房)
 $1413万
 $27,980/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="H11" s="22" t="inlineStr">
@@ -25027,7 +25027,7 @@
           <t>G | 498呎 (2房)
 $1344万
 $26,978/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
       <c r="I11" s="22" t="inlineStr">
@@ -25035,7 +25035,7 @@
           <t>H | 494呎 (2房)
 $1227万
 $24,840/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="J11" s="21" t="inlineStr"/>
@@ -25068,7 +25068,7 @@
           <t>A | 588呎 (2房)
 $1562万
 $26,561/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -25076,7 +25076,7 @@
           <t>B | 496呎 (2房)
 $1333万
 $26,879/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -25084,7 +25084,7 @@
           <t>C | 591呎 (2房)
 $1565万
 $26,487/呎
-(26年-02月-08日)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -25092,7 +25092,7 @@
           <t>D | 448呎 (2房)
 $1083万
 $24,174/呎
-(25年-11月-04日)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -25100,7 +25100,7 @@
           <t>E | 453呎 (2房)
 $1064万
 $23,479/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -25108,7 +25108,7 @@
           <t>F | 505呎 (2房)
 $1309万
 $25,923/呎
-(26年-01月-21日)</t>
+(26年-01月-22日)</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
@@ -25116,7 +25116,7 @@
           <t>G | 498呎 (2房)
 $1248万
 $25,066/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr">
@@ -25124,7 +25124,7 @@
           <t>H | 494呎 (2房)
 $1280万
 $25,915/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="J12" s="21" t="inlineStr"/>
@@ -25157,7 +25157,7 @@
           <t>A | 588呎 (2房)
 $1554万
 $26,429/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -25165,7 +25165,7 @@
           <t>B | 496呎 (2房)
 $1327万
 $26,758/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -25173,7 +25173,7 @@
           <t>C | 591呎 (2房)
 $1578万
 $26,692/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -25181,7 +25181,7 @@
           <t>D | 448呎 (2房)
 $1038万
 $23,165/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -25189,7 +25189,7 @@
           <t>E | 453呎 (2房)
 $1055万
 $23,294/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -25197,7 +25197,7 @@
           <t>F | 505呎 (2房)
 $1299万
 $25,717/呎
-(26年-01月-22日)</t>
+(26年-01月-23日)</t>
         </is>
       </c>
       <c r="H13" s="22" t="inlineStr">
@@ -25205,7 +25205,7 @@
           <t>G | 498呎 (2房)
 $1302万
 $26,149/呎
-(26年-01月-11日)</t>
+(26年-01月-12日)</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr">
@@ -25213,7 +25213,7 @@
           <t>H | 494呎 (2房)
 $1215万
 $24,593/呎
-(26年-01月-14日)</t>
+(26年-01月-15日)</t>
         </is>
       </c>
       <c r="J13" s="21" t="inlineStr"/>
@@ -25223,7 +25223,7 @@
           <t>P1 | 1294呎 (4+房)
 $6061万
 $46,836/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="M13" s="22" t="inlineStr">
@@ -25231,7 +25231,7 @@
           <t>P2 | 1158呎 (4+房)
 $5225万
 $45,123/呎
-(26年-06月-11日)</t>
+(26年-06月-12日)</t>
         </is>
       </c>
     </row>
@@ -25246,7 +25246,7 @@
           <t>A | 588呎 (2房)
 $1449万
 $24,643/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -25254,7 +25254,7 @@
           <t>B | 496呎 (2房)
 $1321万
 $26,639/呎
-(26年-02月-22日)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -25262,7 +25262,7 @@
           <t>C | 591呎 (2房)
 $1570万
 $26,572/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -25270,7 +25270,7 @@
           <t>D | 448呎 (2房)
 $1026万
 $22,891/呎
-(25年-09月-24日)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -25278,7 +25278,7 @@
           <t>E | 453呎 (2房)
 $1047万
 $23,108/呎
-(25年-09月-24日)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -25286,7 +25286,7 @@
           <t>F | 505呎 (2房)
 $1335万
 $26,440/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="H14" s="22" t="inlineStr">
@@ -25294,7 +25294,7 @@
           <t>G | 498呎 (2房)
 $1256万
 $25,217/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr">
@@ -25302,7 +25302,7 @@
           <t>H | 494呎 (2房)
 $1197万
 $24,229/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="J14" s="21" t="inlineStr"/>
@@ -25312,7 +25312,7 @@
           <t>P1 | 1294呎 (4+房)
 $4827万
 $37,300/呎
-(25年-12月-08日)</t>
+(25年-12月-09日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -25335,7 +25335,7 @@
           <t>A | 588呎 (2房)
 $1438万
 $24,459/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -25343,7 +25343,7 @@
           <t>B | 496呎 (2房)
 $1315万
 $26,518/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -25351,7 +25351,7 @@
           <t>C | 591呎 (2房)
 $1563万
 $26,453/呎
-(26年-01月-27日)</t>
+(26年-01月-28日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -25359,7 +25359,7 @@
           <t>D | 448呎 (2房)
 $998万
 $22,268/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -25367,7 +25367,7 @@
           <t>E | 453呎 (2房)
 $1038万
 $22,923/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -25375,7 +25375,7 @@
           <t>F | 505呎 (2房)
 $1278万
 $25,309/呎
-(26年-01月-15日)</t>
+(26年-01月-16日)</t>
         </is>
       </c>
       <c r="H15" s="22" t="inlineStr">
@@ -25383,7 +25383,7 @@
           <t>G | 498呎 (2房)
 $1225万
 $24,594/呎
-(26年-01月-04日)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr">
@@ -25391,7 +25391,7 @@
           <t>H | 494呎 (2房)
 $1174万
 $23,755/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="J15" s="21" t="inlineStr"/>
@@ -25401,7 +25401,7 @@
           <t>P1 | 1294呎 (4+房)
 $5795万
 $44,784/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -25424,7 +25424,7 @@
           <t>A | 588呎 (2房)
 $1428万
 $24,277/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -25432,7 +25432,7 @@
           <t>B | 496呎 (2房)
 $1310万
 $26,401/呎
-(26年-02月-09日)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -25440,7 +25440,7 @@
           <t>C | 591呎 (2房)
 $1556万
 $26,335/呎
-(26年-01月-20日)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -25448,7 +25448,7 @@
           <t>D | 448呎 (2房)
 $991万
 $22,112/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -25456,7 +25456,7 @@
           <t>E | 453呎 (2房)
 $1030万
 $22,742/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -25464,7 +25464,7 @@
           <t>F | 505呎 (2房)
 $1214万
 $24,044/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
@@ -25472,7 +25472,7 @@
           <t>G | 498呎 (2房)
 $1275万
 $25,608/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr">
@@ -25480,7 +25480,7 @@
           <t>H | 494呎 (2房)
 $1128万
 $22,830/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="J16" s="21" t="inlineStr"/>
@@ -25498,7 +25498,7 @@
           <t>P2 | 1158呎 (4+房)
 $4874万
 $42,091/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
     </row>
@@ -25513,7 +25513,7 @@
           <t>A | 588呎 (2房)
 $1417万
 $24,095/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -25521,7 +25521,7 @@
           <t>B | 496呎 (2房)
 $1304万
 $26,282/呎
-(25年-12月-18日)</t>
+(25年-12月-19日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -25529,7 +25529,7 @@
           <t>C | 591呎 (2房)
 $1531万
 $25,898/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -25537,7 +25537,7 @@
           <t>D | 448呎 (2房)
 $984万
 $21,958/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -25545,7 +25545,7 @@
           <t>E | 453呎 (2房)
 $1009万
 $22,280/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -25553,7 +25553,7 @@
           <t>F | 505呎 (2房)
 $1204万
 $23,851/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -25561,7 +25561,7 @@
           <t>G | 498呎 (2房)
 $1208万
 $24,253/呎
-(25年-11月-27日)</t>
+(25年-11月-28日)</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr">
@@ -25569,7 +25569,7 @@
           <t>H | 494呎 (2房)
 $1118万
 $22,626/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="J17" s="21" t="inlineStr"/>
@@ -25579,7 +25579,7 @@
           <t>P1 | 1294呎 (4+房)
 $4609万
 $35,618/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="M17" s="22" t="inlineStr">
@@ -25587,7 +25587,7 @@
           <t>P2 | 1158呎 (4+房)
 $4029万
 $34,791/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
     </row>
@@ -25602,7 +25602,7 @@
           <t>A | 588呎 (2房)
 $1406万
 $23,918/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -25610,7 +25610,7 @@
           <t>B | 496呎 (2房)
 $1306万
 $26,323/呎
-(25年-10月-19日)</t>
+(25年-10月-20日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -25618,7 +25618,7 @@
           <t>C | 591呎 (2房)
 $1552万
 $26,257/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -25626,7 +25626,7 @@
           <t>D | 448呎 (2房)
 $977万
 $21,806/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -25634,7 +25634,7 @@
           <t>E | 453呎 (2房)
 $1001万
 $22,104/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -25642,7 +25642,7 @@
           <t>F | 505呎 (2房)
 $1271万
 $25,160/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -25650,7 +25650,7 @@
           <t>G | 498呎 (2房)
 $1258万
 $25,253/呎
-(25年-11月-17日)</t>
+(25年-11月-18日)</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr">
@@ -25658,7 +25658,7 @@
           <t>H | 494呎 (2房)
 $1108万
 $22,425/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="J18" s="21" t="inlineStr"/>
@@ -25668,7 +25668,7 @@
           <t>P1 | 1294呎 (4+房)
 $4917万
 $38,000/呎
-(26年-02月-24日)</t>
+(26年-02月-25日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -25691,7 +25691,7 @@
           <t>A | 588呎 (2房)
 $1466万
 $24,927/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -25699,7 +25699,7 @@
           <t>B | 496呎 (2房)
 $1294万
 $26,089/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -25707,7 +25707,7 @@
           <t>C | 591呎 (2房)
 $1529万
 $25,868/呎
-(25年-10月-29日)</t>
+(25年-10月-30日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -25715,7 +25715,7 @@
           <t>D | 448呎 (2房)
 $970万
 $21,654/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -25723,7 +25723,7 @@
           <t>E | 453呎 (2房)
 $1004万
 $22,161/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -25731,7 +25731,7 @@
           <t>F | 505呎 (2房)
 $1192万
 $23,608/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -25739,7 +25739,7 @@
           <t>G | 498呎 (2房)
 $1249万
 $25,076/呎
-(25年-11月-16日)</t>
+(25年-11月-17日)</t>
         </is>
       </c>
       <c r="I19" s="22" t="inlineStr">
@@ -25747,7 +25747,7 @@
           <t>H | 494呎 (2房)
 $1098万
 $22,225/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="J19" s="21" t="inlineStr"/>
@@ -25757,7 +25757,7 @@
           <t>P1 | 1294呎 (4+房)
 $5112万
 $39,505/呎
-(26年-02月-19日)</t>
+(26年-02月-20日)</t>
         </is>
       </c>
       <c r="M19" s="22" t="inlineStr">
@@ -25765,7 +25765,7 @@
           <t>P2 | 1158呎 (4+房)
 $4635万
 $40,022/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -25780,7 +25780,7 @@
           <t>A | 588呎 (2房)
 $1455万
 $24,740/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -25788,7 +25788,7 @@
           <t>B | 496呎 (2房)
 $1275万
 $25,700/呎
-(25年-12月-07日)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -25796,7 +25796,7 @@
           <t>C | 591呎 (2房)
 $1515万
 $25,636/呎
-(25年-12月-03日)</t>
+(25年-12月-04日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -25804,7 +25804,7 @@
           <t>D | 448呎 (2房)
 $1012万
 $22,578/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -25812,7 +25812,7 @@
           <t>E | 453呎 (2房)
 $996万
 $21,987/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -25820,7 +25820,7 @@
           <t>F | 505呎 (2房)
 $1183万
 $23,422/呎
-(25年-10月-14日)</t>
+(25年-10月-15日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -25828,7 +25828,7 @@
           <t>G | 498呎 (2房)
 $1183万
 $23,751/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr">
@@ -25836,7 +25836,7 @@
           <t>H | 494呎 (2房)
 $1088万
 $22,026/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="J20" s="21" t="inlineStr"/>
@@ -25846,7 +25846,7 @@
           <t>P1 | 1294呎 (4+房)
 $4428万
 $34,219/呎
-(25年-10月-13日)</t>
+(25年-10月-14日)</t>
         </is>
       </c>
       <c r="M20" s="22" t="inlineStr">
@@ -25854,7 +25854,7 @@
           <t>P2 | 1158呎 (4+房)
 $4461万
 $38,522/呎
-(26年-03月-16日)</t>
+(26年-03月-17日)</t>
         </is>
       </c>
     </row>
@@ -25869,7 +25869,7 @@
           <t>A | 588呎 (2房)
 $1444万
 $24,556/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -25877,7 +25877,7 @@
           <t>B | 496呎 (2房)
 $1225万
 $24,700/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -25885,7 +25885,7 @@
           <t>C | 591呎 (2房)
 $1502万
 $25,406/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -25893,7 +25893,7 @@
           <t>D | 448呎 (2房)
 $957万
 $21,355/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -25901,7 +25901,7 @@
           <t>E | 453呎 (2房)
 $988万
 $21,810/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -25909,7 +25909,7 @@
           <t>F | 505呎 (2房)
 $1173万
 $23,236/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -25917,7 +25917,7 @@
           <t>G | 498呎 (2房)
 $1175万
 $23,586/呎
-(25年-10月-27日)</t>
+(25年-10月-28日)</t>
         </is>
       </c>
       <c r="I21" s="22" t="inlineStr">
@@ -25925,7 +25925,7 @@
           <t>H | 494呎 (2房)
 $1132万
 $22,921/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="J21" s="21" t="inlineStr"/>
@@ -25935,7 +25935,7 @@
           <t>P1 | 1294呎 (4+房)
 $4859万
 $37,550/呎
-(26年-02月-03日)</t>
+(26年-02月-04日)</t>
         </is>
       </c>
       <c r="M21" s="22" t="inlineStr">
@@ -25943,7 +25943,7 @@
           <t>P2 | 1158呎 (4+房)
 $3972万
 $34,300/呎
-(26年-03月-09日)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
     </row>
@@ -25958,7 +25958,7 @@
           <t>A | 586呎 (2房)
 $1360万
 $23,213/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -25966,7 +25966,7 @@
           <t>B | 497呎 (2房)
 $1315万
 $26,467/呎
-(25年-11月-25日)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -25974,7 +25974,7 @@
           <t>C | 591呎 (2房)
 $1488万
 $25,181/呎
-(25年-12月-09日)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -25982,7 +25982,7 @@
           <t>D | 448呎 (2房)
 $998万
 $22,266/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -25990,7 +25990,7 @@
           <t>E | 453呎 (2房)
 $980万
 $21,638/呎
-(25年-09月-21日)</t>
+(25年-09月-22日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -25998,7 +25998,7 @@
           <t>F | 505呎 (2房)
 $1164万
 $23,050/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -26006,7 +26006,7 @@
           <t>G | 502呎 (2房)
 $1140万
 $22,713/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr">
@@ -26014,7 +26014,7 @@
           <t>H | 498呎 (2房)
 $1071万
 $21,508/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="J22" s="22" t="inlineStr">
@@ -26022,7 +26022,7 @@
           <t>J | 480呎 (2房)
 $1030万
 $21,460/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="K22" s="22" t="inlineStr">
@@ -26030,7 +26030,7 @@
           <t>K | 507呎 (2房)
 $1152万
 $22,714/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="L22" s="22" t="inlineStr">
@@ -26038,7 +26038,7 @@
           <t>P1 | 778呎 (3房)
 $2287万
 $29,400/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="M22" s="22" t="inlineStr">
@@ -26046,7 +26046,7 @@
           <t>P2 | 759呎 (3房)
 $2209万
 $29,100/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
     </row>
@@ -26061,7 +26061,7 @@
           <t>A | 586呎 (2房)
 $1350万
 $23,039/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -26069,7 +26069,7 @@
           <t>B | 497呎 (2房)
 $1243万
 $25,018/呎
-(25年-10月-21日)</t>
+(25年-10月-22日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -26077,7 +26077,7 @@
           <t>C | 591呎 (2房)
 $1430万
 $24,200/呎
-(25年-10月-22日)</t>
+(25年-10月-23日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -26085,7 +26085,7 @@
           <t>D | 448呎 (2房)
 $992万
 $22,154/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -26093,7 +26093,7 @@
           <t>E | 453呎 (2房)
 $975万
 $21,530/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -26101,7 +26101,7 @@
           <t>F | 505呎 (2房)
 $1158万
 $22,937/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -26109,7 +26109,7 @@
           <t>G | 502呎 (2房)
 $1170万
 $23,307/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="I23" s="22" t="inlineStr">
@@ -26117,7 +26117,7 @@
           <t>H | 498呎 (2房)
 $1119万
 $22,470/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="J23" s="22" t="inlineStr">
@@ -26125,7 +26125,7 @@
           <t>J | 480呎 (2房)
 $1035万
 $21,558/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="K23" s="22" t="inlineStr">
@@ -26133,7 +26133,7 @@
           <t>K | 507呎 (2房)
 $1146万
 $22,600/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="L23" s="22" t="inlineStr">
@@ -26141,7 +26141,7 @@
           <t>P1 | 778呎 (3房)
 $2264万
 $29,100/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="M23" s="22" t="inlineStr">
@@ -26149,7 +26149,7 @@
           <t>P2 | 759呎 (3房)
 $2391万
 $31,501/呎
-(26年-01月-05日)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
     </row>
@@ -26164,7 +26164,7 @@
           <t>A | 586呎 (2房)
 $1338万
 $22,834/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -26172,7 +26172,7 @@
           <t>B | 497呎 (2房)
 $1198万
 $24,115/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -26180,7 +26180,7 @@
           <t>C | 591呎 (2房)
 $1493万
 $25,259/呎
-(25年-10月-15日)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -26188,7 +26188,7 @@
           <t>D | 448呎 (2房)
 $988万
 $22,045/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -26196,7 +26196,7 @@
           <t>E | 453呎 (2房)
 $970万
 $21,422/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -26204,7 +26204,7 @@
           <t>F | 505呎 (2房)
 $1152万
 $22,822/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H24" s="22" t="inlineStr">
@@ -26212,7 +26212,7 @@
           <t>G | 502呎 (2房)
 $1164万
 $23,189/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="I24" s="22" t="inlineStr">
@@ -26220,7 +26220,7 @@
           <t>H | 498呎 (2房)
 $1060万
 $21,293/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="J24" s="22" t="inlineStr">
@@ -26228,7 +26228,7 @@
           <t>J | 480呎 (2房)
 $1068万
 $22,254/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="K24" s="22" t="inlineStr">
@@ -26236,7 +26236,7 @@
           <t>K | 507呎 (2房)
 $1140万
 $22,487/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="L24" s="22" t="inlineStr">
@@ -26244,7 +26244,7 @@
           <t>P1 | 778呎 (3房)
 $2241万
 $28,799/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="M24" s="22" t="inlineStr">
@@ -26252,7 +26252,7 @@
           <t>P2 | 759呎 (3房)
 $2194万
 $28,900/呎
-(25年-10月-30日)</t>
+(25年-10月-31日)</t>
         </is>
       </c>
     </row>
@@ -26267,7 +26267,7 @@
           <t>A | 586呎 (2房)
 $1326万
 $22,631/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -26275,7 +26275,7 @@
           <t>B | 497呎 (2房)
 $1191万
 $23,972/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -26283,7 +26283,7 @@
           <t>C | 591呎 (2房)
 $1413万
 $23,912/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -26291,7 +26291,7 @@
           <t>D | 448呎 (2房)
 $936万
 $20,891/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -26299,7 +26299,7 @@
           <t>E | 453呎 (2房)
 $1014万
 $22,382/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -26307,7 +26307,7 @@
           <t>F | 505呎 (2房)
 $1147万
 $22,709/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="H25" s="22" t="inlineStr">
@@ -26315,7 +26315,7 @@
           <t>G | 502呎 (2房)
 $1179万
 $23,494/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="I25" s="22" t="inlineStr">
@@ -26323,7 +26323,7 @@
           <t>H | 498呎 (2房)
 $1108万
 $22,247/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="J25" s="22" t="inlineStr">
@@ -26331,7 +26331,7 @@
           <t>J | 480呎 (2房)
 $1063万
 $22,144/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="K25" s="22" t="inlineStr">
@@ -26339,7 +26339,7 @@
           <t>K | 507呎 (2房)
 $1134万
 $22,375/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="L25" s="22" t="inlineStr">
@@ -26347,7 +26347,7 @@
           <t>P1 | 778呎 (3房)
 $2217万
 $28,500/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="M25" s="22" t="inlineStr">
@@ -26355,7 +26355,7 @@
           <t>P2 | 759呎 (3房)
 $2155万
 $28,395/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
     </row>
@@ -26370,7 +26370,7 @@
           <t>A | 586呎 (2房)
 $1377万
 $23,502/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -26378,7 +26378,7 @@
           <t>B | 497呎 (2房)
 $1244万
 $25,020/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -26386,7 +26386,7 @@
           <t>C | 591呎 (2房)
 $1405万
 $23,770/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -26394,7 +26394,7 @@
           <t>D | 448呎 (2房)
 $931万
 $20,786/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -26402,7 +26402,7 @@
           <t>E | 453呎 (2房)
 $1009万
 $22,272/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="G26" s="22" t="inlineStr">
@@ -26410,7 +26410,7 @@
           <t>F | 505呎 (2房)
 $1141万
 $22,596/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="H26" s="22" t="inlineStr">
@@ -26418,7 +26418,7 @@
           <t>G | 502呎 (2房)
 $1174万
 $23,376/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="I26" s="22" t="inlineStr">
@@ -26426,7 +26426,7 @@
           <t>H | 498呎 (2房)
 $1050万
 $21,082/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="J26" s="22" t="inlineStr">
@@ -26434,7 +26434,7 @@
           <t>J | 480呎 (2房)
 $1007万
 $20,983/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K26" s="22" t="inlineStr">
@@ -26442,7 +26442,7 @@
           <t>K | 507呎 (2房)
 $1129万
 $22,264/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="L26" s="22" t="inlineStr">
@@ -26450,7 +26450,7 @@
           <t>P1 | 778呎 (3房)
 $2194万
 $28,201/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="M26" s="22" t="inlineStr">
@@ -26458,7 +26458,7 @@
           <t>P2 | 759呎 (3房)
 $2221万
 $29,264/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -26473,7 +26473,7 @@
           <t>A | 586呎 (2房)
 $1305万
 $22,271/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C27" s="22" t="inlineStr">
@@ -26481,7 +26481,7 @@
           <t>B | 497呎 (2房)
 $1177万
 $23,686/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="D27" s="22" t="inlineStr">
@@ -26489,7 +26489,7 @@
           <t>C | 591呎 (2房)
 $1396万
 $23,628/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -26497,7 +26497,7 @@
           <t>D | 448呎 (2房)
 $927万
 $20,683/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="F27" s="22" t="inlineStr">
@@ -26505,7 +26505,7 @@
           <t>E | 453呎 (2房)
 $956万
 $21,104/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="G27" s="22" t="inlineStr">
@@ -26513,7 +26513,7 @@
           <t>F | 505呎 (2房)
 $1135万
 $22,483/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="H27" s="22" t="inlineStr">
@@ -26521,7 +26521,7 @@
           <t>G | 502呎 (2房)
 $1112万
 $22,153/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="I27" s="22" t="inlineStr">
@@ -26529,7 +26529,7 @@
           <t>H | 498呎 (2房)
 $1097万
 $22,026/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="J27" s="22" t="inlineStr">
@@ -26537,7 +26537,7 @@
           <t>J | 480呎 (2房)
 $1002万
 $20,879/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="K27" s="22" t="inlineStr">
@@ -26545,7 +26545,7 @@
           <t>K | 507呎 (2房)
 $1123万
 $22,154/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="L27" s="22" t="inlineStr">
@@ -26553,7 +26553,7 @@
           <t>P1 | 778呎 (3房)
 $2293万
 $29,474/呎
-(25年-10月-12日)</t>
+(25年-10月-13日)</t>
         </is>
       </c>
       <c r="M27" s="22" t="inlineStr">
@@ -26561,7 +26561,7 @@
           <t>P2 | 759呎 (3房)
 $2273万
 $29,950/呎
-(25年-12月-28日)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
     </row>
@@ -26576,7 +26576,7 @@
           <t>A | 586呎 (2房)
 $1299万
 $22,160/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -26584,7 +26584,7 @@
           <t>B | 497呎 (2房)
 $1157万
 $23,274/呎
-(25年-09月-09日)</t>
+(25年-09月-10日)</t>
         </is>
       </c>
       <c r="D28" s="22" t="inlineStr">
@@ -26592,7 +26592,7 @@
           <t>C | 591呎 (2房)
 $1388万
 $23,486/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -26600,7 +26600,7 @@
           <t>D | 448呎 (2房)
 $922万
 $20,580/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="F28" s="22" t="inlineStr">
@@ -26608,7 +26608,7 @@
           <t>E | 453呎 (2房)
 $951万
 $21,000/呎
-(25年-08月-31日)</t>
+(25年-09月-01日)</t>
         </is>
       </c>
       <c r="G28" s="22" t="inlineStr">
@@ -26616,7 +26616,7 @@
           <t>F | 505呎 (2房)
 $1130万
 $22,370/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="H28" s="22" t="inlineStr">
@@ -26624,7 +26624,7 @@
           <t>G | 502呎 (2房)
 $1107万
 $22,044/呎
-(25年-10月-05日)</t>
+(25年-10月-06日)</t>
         </is>
       </c>
       <c r="I28" s="22" t="inlineStr">
@@ -26632,7 +26632,7 @@
           <t>H | 498呎 (2房)
 $1040万
 $20,873/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="J28" s="22" t="inlineStr">
@@ -26640,7 +26640,7 @@
           <t>J | 480呎 (2房)
 $997万
 $20,775/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="K28" s="22" t="inlineStr">
@@ -26648,7 +26648,7 @@
           <t>K | 507呎 (2房)
 $1118万
 $22,043/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="L28" s="22" t="inlineStr">
@@ -26656,7 +26656,7 @@
           <t>P1 | 778呎 (3房)
 $2129万
 $27,361/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="M28" s="22" t="inlineStr">
@@ -26664,7 +26664,7 @@
           <t>P2 | 759呎 (3房)
 $2121万
 $27,947/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
     </row>
@@ -26679,7 +26679,7 @@
           <t>A | 586呎 (2房)
 $1357万
 $23,152/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="C29" s="22" t="inlineStr">
@@ -26687,7 +26687,7 @@
           <t>B | 497呎 (2房)
 $1139万
 $22,909/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="D29" s="22" t="inlineStr">
@@ -26695,7 +26695,7 @@
           <t>C | 591呎 (2房)
 $1380万
 $23,347/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="E29" s="22" t="inlineStr">
@@ -26703,7 +26703,7 @@
           <t>D | 448呎 (2房)
 $963万
 $21,502/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="F29" s="22" t="inlineStr">
@@ -26711,7 +26711,7 @@
           <t>E | 453呎 (2房)
 $994万
 $21,938/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="G29" s="22" t="inlineStr">
@@ -26719,7 +26719,7 @@
           <t>F | 505呎 (2房)
 $1124万
 $22,259/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="H29" s="22" t="inlineStr">
@@ -26727,7 +26727,7 @@
           <t>G | 502呎 (2房)
 $1101万
 $21,934/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="I29" s="22" t="inlineStr">
@@ -26735,7 +26735,7 @@
           <t>H | 498呎 (2房)
 $1034万
 $20,769/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="J29" s="22" t="inlineStr">
@@ -26743,7 +26743,7 @@
           <t>J | 480呎 (2房)
 $992万
 $20,673/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="K29" s="22" t="inlineStr">
@@ -26751,7 +26751,7 @@
           <t>K | 507呎 (2房)
 $1168万
 $23,030/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="L29" s="22" t="inlineStr">
@@ -26759,7 +26759,7 @@
           <t>P1 | 778呎 (3房)
 $2112万
 $27,144/呎
-(25年-09月-16日)</t>
+(25年-09月-17日)</t>
         </is>
       </c>
       <c r="M29" s="22" t="inlineStr">
@@ -26767,7 +26767,7 @@
           <t>P2 | 759呎 (3房)
 $2032万
 $26,771/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
     </row>
@@ -26782,7 +26782,7 @@
           <t>A | 586呎 (2房)
 $1286万
 $21,940/呎
-(25年-08月-13日)</t>
+(25年-08月-14日)</t>
         </is>
       </c>
       <c r="C30" s="22" t="inlineStr">
@@ -26790,7 +26790,7 @@
           <t>B | 497呎 (2房)
 $1184万
 $23,817/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="D30" s="22" t="inlineStr">
@@ -26798,7 +26798,7 @@
           <t>C | 591呎 (2房)
 $1372万
 $23,208/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="E30" s="22" t="inlineStr">
@@ -26806,7 +26806,7 @@
           <t>D | 448呎 (2房)
 $913万
 $20,375/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="F30" s="22" t="inlineStr">
@@ -26814,7 +26814,7 @@
           <t>E | 453呎 (2房)
 $942万
 $20,792/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="G30" s="22" t="inlineStr">
@@ -26822,7 +26822,7 @@
           <t>F | 505呎 (2房)
 $1118万
 $22,149/呎
-(25年-09月-01日)</t>
+(25年-09月-02日)</t>
         </is>
       </c>
       <c r="H30" s="22" t="inlineStr">
@@ -26830,7 +26830,7 @@
           <t>G | 502呎 (2房)
 $1096万
 $21,825/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="I30" s="22" t="inlineStr">
@@ -26838,7 +26838,7 @@
           <t>H | 498呎 (2房)
 $1029万
 $20,667/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="J30" s="22" t="inlineStr">
@@ -26846,7 +26846,7 @@
           <t>J | 480呎 (2房)
 $987万
 $20,569/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="K30" s="22" t="inlineStr">
@@ -26854,7 +26854,7 @@
           <t>K | 507呎 (2房)
 $1106万
 $21,824/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="L30" s="22" t="inlineStr">
@@ -26862,7 +26862,7 @@
           <t>P1 | 778呎 (3房)
 $2095万
 $26,929/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="M30" s="22" t="inlineStr">
@@ -26870,7 +26870,7 @@
           <t>P2 | 759呎 (3房)
 $2016万
 $26,557/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
     </row>
@@ -26885,7 +26885,7 @@
           <t>A | 586呎 (2房)
 $1279万
 $21,831/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="C31" s="22" t="inlineStr">
@@ -26893,7 +26893,7 @@
           <t>B | 497呎 (2房)
 $1116万
 $22,459/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="D31" s="22" t="inlineStr">
@@ -26901,7 +26901,7 @@
           <t>C | 591呎 (2房)
 $1363万
 $23,069/呎
-(25年-09月-18日)</t>
+(25年-09月-19日)</t>
         </is>
       </c>
       <c r="E31" s="22" t="inlineStr">
@@ -26909,7 +26909,7 @@
           <t>D | 448呎 (2房)
 $908万
 $20,275/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="F31" s="22" t="inlineStr">
@@ -26917,7 +26917,7 @@
           <t>E | 453呎 (2房)
 $937万
 $20,689/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="G31" s="22" t="inlineStr">
@@ -26925,7 +26925,7 @@
           <t>F | 505呎 (2房)
 $1155万
 $22,865/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H31" s="22" t="inlineStr">
@@ -26933,7 +26933,7 @@
           <t>G | 502呎 (2房)
 $1090万
 $21,715/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="I31" s="22" t="inlineStr">
@@ -26941,7 +26941,7 @@
           <t>H | 498呎 (2房)
 $1024万
 $20,562/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="J31" s="22" t="inlineStr">
@@ -26949,7 +26949,7 @@
           <t>J | 480呎 (2房)
 $982万
 $20,467/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K31" s="22" t="inlineStr">
@@ -26957,7 +26957,7 @@
           <t>K | 507呎 (2房)
 $1156万
 $22,801/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="L31" s="22" t="inlineStr">
@@ -26965,7 +26965,7 @@
           <t>P1 | 778呎 (3房)
 $2078万
 $26,715/呎
-(25年-09月-03日)</t>
+(25年-09月-04日)</t>
         </is>
       </c>
       <c r="M31" s="22" t="inlineStr">
@@ -26973,7 +26973,7 @@
           <t>P2 | 759呎 (3房)
 $2000万
 $26,347/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
     </row>
@@ -26988,7 +26988,7 @@
           <t>A | 586呎 (2房)
 $1273万
 $21,722/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C32" s="22" t="inlineStr">
@@ -26996,7 +26996,7 @@
           <t>B | 497呎 (2房)
 $1105万
 $22,237/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D32" s="22" t="inlineStr">
@@ -27004,7 +27004,7 @@
           <t>C | 591呎 (2房)
 $1322万
 $22,372/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="E32" s="22" t="inlineStr">
@@ -27012,7 +27012,7 @@
           <t>D | 448呎 (2房)
 $904万
 $20,174/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="F32" s="22" t="inlineStr">
@@ -27020,7 +27020,7 @@
           <t>E | 453呎 (2房)
 $979万
 $21,614/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="G32" s="22" t="inlineStr">
@@ -27028,7 +27028,7 @@
           <t>F | 505呎 (2房)
 $1107万
 $21,929/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="H32" s="22" t="inlineStr">
@@ -27036,7 +27036,7 @@
           <t>G | 502呎 (2房)
 $1085万
 $21,608/呎
-(25年-09月-14日)</t>
+(25年-09月-15日)</t>
         </is>
       </c>
       <c r="I32" s="22" t="inlineStr">
@@ -27044,7 +27044,7 @@
           <t>H | 498呎 (2房)
 $1070万
 $21,484/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="J32" s="22" t="inlineStr">
@@ -27052,7 +27052,7 @@
           <t>J | 480呎 (2房)
 $1026万
 $21,383/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K32" s="22" t="inlineStr">
@@ -27060,7 +27060,7 @@
           <t>K | 507呎 (2房)
 $1150万
 $22,688/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="L32" s="22" t="inlineStr">
@@ -27068,7 +27068,7 @@
           <t>P1 | 778呎 (3房)
 $2156万
 $27,719/呎
-(25年-08月-11日)</t>
+(25年-08月-12日)</t>
         </is>
       </c>
       <c r="M32" s="22" t="inlineStr">
@@ -27076,7 +27076,7 @@
           <t>P2 | 759呎 (3房)
 $2075万
 $27,336/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -27091,7 +27091,7 @@
           <t>A | 586呎 (2房)
 $1267万
 $21,614/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C33" s="22" t="inlineStr">
@@ -27099,7 +27099,7 @@
           <t>B | 497呎 (2房)
 $1094万
 $22,016/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="D33" s="22" t="inlineStr">
@@ -27107,7 +27107,7 @@
           <t>C | 591呎 (2房)
 $1316万
 $22,261/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="E33" s="22" t="inlineStr">
@@ -27115,7 +27115,7 @@
           <t>D | 448呎 (2房)
 $899万
 $20,074/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="F33" s="22" t="inlineStr">
@@ -27123,7 +27123,7 @@
           <t>E | 453呎 (2房)
 $974万
 $21,508/呎
-(25年-09月-11日)</t>
+(25年-09月-12日)</t>
         </is>
       </c>
       <c r="G33" s="22" t="inlineStr">
@@ -27131,7 +27131,7 @@
           <t>F | 505呎 (2房)
 $1102万
 $21,820/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="H33" s="22" t="inlineStr">
@@ -27139,7 +27139,7 @@
           <t>G | 502呎 (2房)
 $1079万
 $21,500/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I33" s="22" t="inlineStr">
@@ -27147,7 +27147,7 @@
           <t>H | 498呎 (2房)
 $1014万
 $20,359/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="J33" s="22" t="inlineStr">
@@ -27155,7 +27155,7 @@
           <t>J | 480呎 (2房)
 $973万
 $20,265/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="K33" s="22" t="inlineStr">
@@ -27163,7 +27163,7 @@
           <t>K | 507呎 (2房)
 $1144万
 $22,574/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="L33" s="22" t="inlineStr">
@@ -27171,7 +27171,7 @@
           <t>P1 | 778呎 (3房)
 $2038万
 $26,189/呎
-(25年-08月-10日)</t>
+(25年-08月-11日)</t>
         </is>
       </c>
       <c r="M33" s="22" t="inlineStr">
@@ -27179,7 +27179,7 @@
           <t>P2 | 759呎 (3房)
 $1960万
 $25,829/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
     </row>
@@ -27194,7 +27194,7 @@
           <t>A | 586呎 (2房)
 $1260万
 $21,507/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C34" s="22" t="inlineStr">
@@ -27202,7 +27202,7 @@
           <t>B | 497呎 (2房)
 $1055万
 $21,219/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D34" s="22" t="inlineStr">
@@ -27210,7 +27210,7 @@
           <t>C | 591呎 (2房)
 $1374万
 $23,257/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E34" s="22" t="inlineStr">
@@ -27218,7 +27218,7 @@
           <t>D | 448呎 (2房)
 $895万
 $19,973/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="F34" s="22" t="inlineStr">
@@ -27226,7 +27226,7 @@
           <t>E | 453呎 (2房)
 $923万
 $20,380/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="G34" s="22" t="inlineStr">
@@ -27234,7 +27234,7 @@
           <t>F | 505呎 (2房)
 $1096万
 $21,711/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H34" s="22" t="inlineStr">
@@ -27242,7 +27242,7 @@
           <t>G | 502呎 (2房)
 $1074万
 $21,394/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="I34" s="22" t="inlineStr">
@@ -27250,7 +27250,7 @@
           <t>H | 498呎 (2房)
 $1009万
 $20,257/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="J34" s="22" t="inlineStr">
@@ -27258,7 +27258,7 @@
           <t>J | 480呎 (2房)
 $968万
 $20,162/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K34" s="22" t="inlineStr">
@@ -27266,7 +27266,7 @@
           <t>K | 507呎 (2房)
 $1085万
 $21,394/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="L34" s="22" t="inlineStr">
@@ -27274,7 +27274,7 @@
           <t>P1 | 778呎 (3房)
 $2186万
 $28,091/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M34" s="22" t="inlineStr">
@@ -27282,7 +27282,7 @@
           <t>P2 | 759呎 (3房)
 $1945万
 $25,623/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
     </row>
@@ -27297,7 +27297,7 @@
           <t>A | 586呎 (2房)
 $1254万
 $21,399/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="C35" s="22" t="inlineStr">
@@ -27305,7 +27305,7 @@
           <t>B | 497呎 (2房)
 $1102万
 $22,183/呎
-(25年-07月-24日)</t>
+(25年-07月-25日)</t>
         </is>
       </c>
       <c r="D35" s="22" t="inlineStr">
@@ -27313,7 +27313,7 @@
           <t>C | 591呎 (2房)
 $1303万
 $22,041/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E35" s="22" t="inlineStr">
@@ -27321,7 +27321,7 @@
           <t>D | 448呎 (2房)
 $890万
 $19,875/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="F35" s="22" t="inlineStr">
@@ -27329,7 +27329,7 @@
           <t>E | 453呎 (2房)
 $919万
 $20,280/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="G35" s="22" t="inlineStr">
@@ -27337,7 +27337,7 @@
           <t>F | 505呎 (2房)
 $1091万
 $21,604/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H35" s="22" t="inlineStr">
@@ -27345,7 +27345,7 @@
           <t>G | 502呎 (2房)
 $1069万
 $21,287/呎
-(25年-10月-08日)</t>
+(25年-10月-09日)</t>
         </is>
       </c>
       <c r="I35" s="22" t="inlineStr">
@@ -27353,7 +27353,7 @@
           <t>H | 498呎 (2房)
 $1004万
 $20,157/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="J35" s="22" t="inlineStr">
@@ -27361,7 +27361,7 @@
           <t>J | 480呎 (2房)
 $963万
 $20,062/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
       <c r="K35" s="22" t="inlineStr">
@@ -27369,7 +27369,7 @@
           <t>K | 507呎 (2房)
 $1079万
 $21,286/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="L35" s="22" t="inlineStr">
@@ -27377,7 +27377,7 @@
           <t>P1 | 778呎 (3房)
 $2077万
 $26,700/呎
-(25年-11月-05日)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="M35" s="22" t="inlineStr">
@@ -27385,7 +27385,7 @@
           <t>P2 | 759呎 (3房)
 $2163万
 $28,501/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
     </row>
@@ -27400,7 +27400,7 @@
           <t>A | 586呎 (2房)
 $1248万
 $21,294/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="C36" s="22" t="inlineStr">
@@ -27408,7 +27408,7 @@
           <t>B | 497呎 (2房)
 $1110万
 $22,340/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D36" s="22" t="inlineStr">
@@ -27416,7 +27416,7 @@
           <t>C | 591呎 (2房)
 $1296万
 $21,931/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E36" s="22" t="inlineStr">
@@ -27424,7 +27424,7 @@
           <t>D | 448呎 (2房)
 $886万
 $19,777/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="F36" s="22" t="inlineStr">
@@ -27432,7 +27432,7 @@
           <t>E | 453呎 (2房)
 $960万
 $21,185/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="G36" s="22" t="inlineStr">
@@ -27440,7 +27440,7 @@
           <t>F | 505呎 (2房)
 $1140万
 $22,570/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="H36" s="22" t="inlineStr">
@@ -27448,7 +27448,7 @@
           <t>G | 502呎 (2房)
 $1063万
 $21,181/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I36" s="22" t="inlineStr">
@@ -27456,7 +27456,7 @@
           <t>H | 498呎 (2房)
 $999万
 $20,056/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="J36" s="22" t="inlineStr">
@@ -27464,7 +27464,7 @@
           <t>J | 480呎 (2房)
 $958万
 $19,962/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="K36" s="22" t="inlineStr">
@@ -27472,7 +27472,7 @@
           <t>K | 507呎 (2房)
 $1074万
 $21,181/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="L36" s="22" t="inlineStr">
@@ -27480,7 +27480,7 @@
           <t>P1 | 778呎 (3房)
 $2140万
 $27,500/呎
-(25年-11月-24日)</t>
+(25年-11月-25日)</t>
         </is>
       </c>
       <c r="M36" s="22" t="inlineStr">
@@ -27488,7 +27488,7 @@
           <t>P2 | 759呎 (3房)
 $2148万
 $28,300/呎
-(26年-01月-13日)</t>
+(26年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -27503,7 +27503,7 @@
           <t>A | 586呎 (2房)
 $1238万
 $21,125/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="C37" s="22" t="inlineStr">
@@ -27511,7 +27511,7 @@
           <t>B | 497呎 (2房)
 $1049万
 $21,107/呎
-(25年-08月-18日)</t>
+(25年-08月-19日)</t>
         </is>
       </c>
       <c r="D37" s="22" t="inlineStr">
@@ -27519,7 +27519,7 @@
           <t>C | 591呎 (2房)
 $1290万
 $21,821/呎
-(25年-08月-20日)</t>
+(25年-08月-21日)</t>
         </is>
       </c>
       <c r="E37" s="22" t="inlineStr">
@@ -27527,7 +27527,7 @@
           <t>D | 448呎 (2房)
 $879万
 $19,618/呎
-(25年-08月-19日)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="F37" s="22" t="inlineStr">
@@ -27535,7 +27535,7 @@
           <t>E | 453呎 (2房)
 $907万
 $20,018/呎
-(25年-09月-02日)</t>
+(25年-09月-03日)</t>
         </is>
       </c>
       <c r="G37" s="22" t="inlineStr">
@@ -27543,7 +27543,7 @@
           <t>F | 505呎 (2房)
 $1077万
 $21,325/呎
-(25年-09月-04日)</t>
+(25年-09月-05日)</t>
         </is>
       </c>
       <c r="H37" s="22" t="inlineStr">
@@ -27551,7 +27551,7 @@
           <t>G | 502呎 (2房)
 $1055万
 $21,012/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I37" s="22" t="inlineStr">
@@ -27559,7 +27559,7 @@
           <t>H | 498呎 (2房)
 $1040万
 $20,894/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="J37" s="22" t="inlineStr">
@@ -27567,7 +27567,7 @@
           <t>J | 480呎 (2房)
 $998万
 $20,794/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="K37" s="22" t="inlineStr">
@@ -27575,7 +27575,7 @@
           <t>K | 507呎 (2房)
 $1065万
 $21,014/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="L37" s="22" t="inlineStr">
@@ -27583,7 +27583,7 @@
           <t>P1 | 778呎 (3房)
 $2050万
 $26,350/呎
-(25年-11月-12日)</t>
+(25年-11月-13日)</t>
         </is>
       </c>
       <c r="M37" s="22" t="inlineStr">
@@ -27591,7 +27591,7 @@
           <t>P2 | 759呎 (3房)
 $2269万
 $29,900/呎
-(26年-02月-10日)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
     </row>
@@ -27607,7 +27607,7 @@
           <t>B | 509呎 (2房)
 $1066万
 $20,939/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="D38" s="22" t="inlineStr">
@@ -27615,7 +27615,7 @@
           <t>C | 591呎 (2房)
 $1347万
 $22,799/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="E38" s="22" t="inlineStr">
@@ -27623,7 +27623,7 @@
           <t>D | 448呎 (2房)
 $872万
 $19,464/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="F38" s="22" t="inlineStr">
@@ -27631,7 +27631,7 @@
           <t>E | 453呎 (2房)
 $945万
 $20,852/呎
-(25年-08月-24日)</t>
+(25年-08月-25日)</t>
         </is>
       </c>
       <c r="G38" s="22" t="inlineStr">
@@ -27639,7 +27639,7 @@
           <t>F | 505呎 (2房)
 $1068万
 $21,156/呎
-(25年-09月-24日)</t>
+(25年-09月-25日)</t>
         </is>
       </c>
       <c r="H38" s="22" t="inlineStr">
@@ -27647,7 +27647,7 @@
           <t>G | 502呎 (2房)
 $1046万
 $20,847/呎
-(25年-10月-07日)</t>
+(25年-10月-08日)</t>
         </is>
       </c>
       <c r="I38" s="22" t="inlineStr">
@@ -27655,7 +27655,7 @@
           <t>H | 505呎 (2房)
 $1047万
 $20,727/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="J38" s="22" t="inlineStr">
@@ -27663,7 +27663,7 @@
           <t>J | 480呎 (2房)
 $943万
 $19,648/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="K38" s="22" t="inlineStr">
@@ -27671,7 +27671,7 @@
           <t>K | 507呎 (2房)
 $1057万
 $20,846/呎
-(25年-08月-14日)</t>
+(25年-08月-15日)</t>
         </is>
       </c>
       <c r="L38" s="22" t="inlineStr">
@@ -27679,7 +27679,7 @@
           <t>P1 | 778呎 (3房)
 $2150万
 $27,640/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="M38" s="22" t="inlineStr">
@@ -27687,7 +27687,7 @@
           <t>P2 | 759呎 (3房)
 $2429万
 $32,000/呎
-(26年-03月-17日)</t>
+(26年-03月-18日)</t>
         </is>
       </c>
     </row>
@@ -27703,7 +27703,7 @@
           <t>B | 509呎 (2房)
 $1110万
 $21,811/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D39" s="22" t="inlineStr">
@@ -27711,7 +27711,7 @@
           <t>C | 591呎 (2房)
 $1277万
 $21,604/呎
-(25年-08月-25日)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="E39" s="22" t="inlineStr">
@@ -27719,7 +27719,7 @@
           <t>D | 402呎 (2房)
 $1199万
 $29,818/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="F39" s="22" t="inlineStr">
@@ -27727,7 +27727,7 @@
           <t>E | 407呎 (2房)
 $1188万
 $29,194/呎
-(25年-10月-16日)</t>
+(25年-10月-17日)</t>
         </is>
       </c>
       <c r="G39" s="22" t="inlineStr">
@@ -27735,7 +27735,7 @@
           <t>F | 459呎 (2房)
 $1249万
 $27,207/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="H39" s="22" t="inlineStr">
@@ -27743,7 +27743,7 @@
           <t>G | 455呎 (2房)
 $1356万
 $29,798/呎
-(25年-08月-17日)</t>
+(25年-08月-18日)</t>
         </is>
       </c>
       <c r="I39" s="22" t="inlineStr">
@@ -27751,7 +27751,7 @@
           <t>H | 458呎 (2房)
 $1319万
 $28,799/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="J39" s="22" t="inlineStr">
@@ -27759,7 +27759,7 @@
           <t>J | 433呎 (2房)
 $1241万
 $28,656/呎
-(25年-10月-23日)</t>
+(25年-10月-24日)</t>
         </is>
       </c>
       <c r="K39" s="22" t="inlineStr">
@@ -27767,7 +27767,7 @@
           <t>K | 460呎 (2房)
 $1329万
 $28,887/呎
-(25年-08月-28日)</t>
+(25年-08月-29日)</t>
         </is>
       </c>
       <c r="L39" s="22" t="inlineStr">
@@ -27775,7 +27775,7 @@
           <t>P1 | 778呎 (3房)
 $2473万
 $31,789/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="M39" s="22" t="inlineStr">
@@ -27783,7 +27783,7 @@
           <t>P2 | 759呎 (3房)
 $2520万
 $33,200/呎
-(26年-06月-02日)</t>
+(26年-06月-03日)</t>
         </is>
       </c>
     </row>
